--- a/Dermatoses_Bulleuses_dataset.xlsx
+++ b/Dermatoses_Bulleuses_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raymond.keya\source\repos\GFMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KIMYAÉDITION\source\repos\GFMP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A254163-30C1-4A04-8A08-8D08EC38F3D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13603719-1174-4E99-85EB-CB10F973045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25840" windowHeight="15533" activeTab="1" xr2:uid="{15E60B8E-A9EB-4C8E-B9A6-575A59F00C56}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="24240" windowHeight="13140" xr2:uid="{15E60B8E-A9EB-4C8E-B9A6-575A59F00C56}"/>
   </bookViews>
   <sheets>
     <sheet name="Dermatoses Bulleuses CNHU HKM" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="240">
   <si>
     <t>_id</t>
   </si>
@@ -606,9 +606,6 @@
     <t>RAPPORT DERMATOSES BULLEUSES CNHU HKM</t>
   </si>
   <si>
-    <t>Rapport automatisé basé sur les données brutes soumises à ce projet</t>
-  </si>
-  <si>
     <t>SECTION 1: POPULATION TOTALE</t>
   </si>
   <si>
@@ -813,36 +810,36 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="ADLaM Display"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1126,6 +1123,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-9B4C-4F6B-AA16-DB889DBDD83E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1141,6 +1143,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-9B4C-4F6B-AA16-DB889DBDD83E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1780,6 +1787,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-175C-456C-BDE3-69C77390DE5A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1795,6 +1807,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-175C-456C-BDE3-69C77390DE5A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2434,6 +2451,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-44CE-4B04-8B6E-DB9748292378}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2449,6 +2471,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-44CE-4B04-8B6E-DB9748292378}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3088,6 +3115,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F12F-4167-8DC0-612B25ED9D47}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3103,6 +3135,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F12F-4167-8DC0-612B25ED9D47}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3118,6 +3155,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F12F-4167-8DC0-612B25ED9D47}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3762,6 +3804,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C8DC-4F2C-B527-88C58E9FCDA4}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3777,6 +3824,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-C8DC-4F2C-B527-88C58E9FCDA4}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3792,6 +3844,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-C8DC-4F2C-B527-88C58E9FCDA4}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -6575,6 +6632,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B22E-4419-B143-681A64F21471}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -6590,6 +6652,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B22E-4419-B143-681A64F21471}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -7252,6 +7319,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5C99-4EDE-83D6-779B5E4A6BF1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -7267,6 +7339,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5C99-4EDE-83D6-779B5E4A6BF1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -7282,6 +7359,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5C99-4EDE-83D6-779B5E4A6BF1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -8678,6 +8760,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-39CF-44DE-8FE6-15731CB1C97E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -8693,6 +8780,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-39CF-44DE-8FE6-15731CB1C97E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -21227,14 +21319,14 @@
     <tableColumn id="21" xr3:uid="{AD79F8C5-619A-4177-BDF8-2FE7F1E7E500}" uniqueName="21" name="Dermatose Immunoallergique" queryTableFieldId="21" dataDxfId="1"/>
     <tableColumn id="22" xr3:uid="{5412061F-94F8-446E-86A0-35334F30ACB5}" uniqueName="22" name="Préciser l'autre diagnostic" queryTableFieldId="22" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleDark6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleDark3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Blue">
+    <a:clrScheme name="Violet II">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -21242,34 +21334,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="17406D"/>
+        <a:srgbClr val="632E62"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="DBEFF9"/>
+        <a:srgbClr val="EAE5EB"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="0F6FC6"/>
+        <a:srgbClr val="92278F"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="009DD9"/>
+        <a:srgbClr val="9B57D3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="0BD0D9"/>
+        <a:srgbClr val="755DD9"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="10CF9B"/>
+        <a:srgbClr val="665EB8"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="7CCA62"/>
+        <a:srgbClr val="45A5ED"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="A5C249"/>
+        <a:srgbClr val="5982DB"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="F49100"/>
+        <a:srgbClr val="0066FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="85DFD0"/>
+        <a:srgbClr val="666699"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -21549,32 +21641,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BF6762-9649-44E7-B11C-7BB1AADC5C2A}">
   <dimension ref="A1:V131"/>
-  <sheetFormatPr defaultRowHeight="14.7" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="79.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21642,7 +21734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>715501306</v>
       </c>
@@ -21695,7 +21787,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>715512334</v>
       </c>
@@ -21748,7 +21840,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>715636712</v>
       </c>
@@ -21801,7 +21893,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>715641743</v>
       </c>
@@ -21851,7 +21943,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>718547936</v>
       </c>
@@ -21907,7 +21999,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>718789179</v>
       </c>
@@ -21966,7 +22058,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>718806158</v>
       </c>
@@ -22022,7 +22114,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>718947052</v>
       </c>
@@ -22075,7 +22167,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>719403589</v>
       </c>
@@ -22131,7 +22223,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>719426805</v>
       </c>
@@ -22184,7 +22276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>722449196</v>
       </c>
@@ -22240,7 +22332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>722452001</v>
       </c>
@@ -22290,7 +22382,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>722479386</v>
       </c>
@@ -22343,7 +22435,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>722480056</v>
       </c>
@@ -22399,7 +22491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>722480377</v>
       </c>
@@ -22452,7 +22544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>722480792</v>
       </c>
@@ -22508,7 +22600,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>722482063</v>
       </c>
@@ -22561,7 +22653,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>722619425</v>
       </c>
@@ -22614,7 +22706,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>722622203</v>
       </c>
@@ -22673,7 +22765,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>722625180</v>
       </c>
@@ -22729,7 +22821,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>722627814</v>
       </c>
@@ -22785,7 +22877,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>722803352</v>
       </c>
@@ -22841,7 +22933,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>722805963</v>
       </c>
@@ -22894,7 +22986,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>722807402</v>
       </c>
@@ -22947,7 +23039,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>722809657</v>
       </c>
@@ -23000,7 +23092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>722811313</v>
       </c>
@@ -23050,7 +23142,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>722813656</v>
       </c>
@@ -23106,7 +23198,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>722815699</v>
       </c>
@@ -23159,7 +23251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>722818850</v>
       </c>
@@ -23209,7 +23301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>722820234</v>
       </c>
@@ -23262,7 +23354,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>722821710</v>
       </c>
@@ -23312,7 +23404,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>722825333</v>
       </c>
@@ -23365,7 +23457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>722831716</v>
       </c>
@@ -23415,7 +23507,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>722832781</v>
       </c>
@@ -23468,7 +23560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>722835688</v>
       </c>
@@ -23521,7 +23613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>722837165</v>
       </c>
@@ -23574,7 +23666,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>722839809</v>
       </c>
@@ -23627,7 +23719,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>722904560</v>
       </c>
@@ -23683,7 +23775,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>722905279</v>
       </c>
@@ -23736,7 +23828,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>722906161</v>
       </c>
@@ -23789,7 +23881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>722907257</v>
       </c>
@@ -23842,7 +23934,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>722908296</v>
       </c>
@@ -23895,7 +23987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>722909162</v>
       </c>
@@ -23951,7 +24043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>722910446</v>
       </c>
@@ -24007,7 +24099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>722913007</v>
       </c>
@@ -24063,7 +24155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>723500929</v>
       </c>
@@ -24113,7 +24205,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>723506643</v>
       </c>
@@ -24169,7 +24261,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>723519297</v>
       </c>
@@ -24222,7 +24314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>723528166</v>
       </c>
@@ -24275,7 +24367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>726303830</v>
       </c>
@@ -24328,7 +24420,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>726306825</v>
       </c>
@@ -24384,7 +24476,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>726343086</v>
       </c>
@@ -24437,7 +24529,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>726483329</v>
       </c>
@@ -24490,7 +24582,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>726486061</v>
       </c>
@@ -24543,7 +24635,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>726493855</v>
       </c>
@@ -24596,7 +24688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>726495267</v>
       </c>
@@ -24646,7 +24738,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>726513108</v>
       </c>
@@ -24699,7 +24791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>726515934</v>
       </c>
@@ -24752,7 +24844,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>726521403</v>
       </c>
@@ -24805,7 +24897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>726526577</v>
       </c>
@@ -24855,7 +24947,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>726532569</v>
       </c>
@@ -24905,7 +24997,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>726537104</v>
       </c>
@@ -24955,7 +25047,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>726539838</v>
       </c>
@@ -25008,7 +25100,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>726543699</v>
       </c>
@@ -25061,7 +25153,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>726548975</v>
       </c>
@@ -25114,7 +25206,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>726554261</v>
       </c>
@@ -25167,7 +25259,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>726595677</v>
       </c>
@@ -25220,7 +25312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>726600709</v>
       </c>
@@ -25270,7 +25362,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>726604770</v>
       </c>
@@ -25320,7 +25412,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>726607612</v>
       </c>
@@ -25370,7 +25462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>726613688</v>
       </c>
@@ -25420,7 +25512,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>726618268</v>
       </c>
@@ -25470,7 +25562,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>727067760</v>
       </c>
@@ -25523,7 +25615,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>727075917</v>
       </c>
@@ -25573,7 +25665,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>727075927</v>
       </c>
@@ -25623,7 +25715,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>727075931</v>
       </c>
@@ -25673,7 +25765,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>727075934</v>
       </c>
@@ -25723,7 +25815,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>727075938</v>
       </c>
@@ -25773,7 +25865,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>727169159</v>
       </c>
@@ -25823,7 +25915,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>727169164</v>
       </c>
@@ -25876,7 +25968,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>727169171</v>
       </c>
@@ -25929,7 +26021,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>727169173</v>
       </c>
@@ -25979,7 +26071,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>727169177</v>
       </c>
@@ -26029,7 +26121,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>727254557</v>
       </c>
@@ -26082,7 +26174,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>727363670</v>
       </c>
@@ -26135,7 +26227,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>727368762</v>
       </c>
@@ -26188,7 +26280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>727375146</v>
       </c>
@@ -26238,7 +26330,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>727381382</v>
       </c>
@@ -26291,7 +26383,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>727387342</v>
       </c>
@@ -26341,7 +26433,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>727394807</v>
       </c>
@@ -26394,7 +26486,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>727401585</v>
       </c>
@@ -26444,7 +26536,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>727409977</v>
       </c>
@@ -26497,7 +26589,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>727417895</v>
       </c>
@@ -26547,7 +26639,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>727422558</v>
       </c>
@@ -26597,7 +26689,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>727427192</v>
       </c>
@@ -26650,7 +26742,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>727560327</v>
       </c>
@@ -26703,7 +26795,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>727564575</v>
       </c>
@@ -26756,7 +26848,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>727575819</v>
       </c>
@@ -26806,7 +26898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>727580014</v>
       </c>
@@ -26856,7 +26948,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>727583780</v>
       </c>
@@ -26906,7 +26998,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>727587593</v>
       </c>
@@ -26959,7 +27051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>727587971</v>
       </c>
@@ -27009,7 +27101,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>727591779</v>
       </c>
@@ -27062,7 +27154,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>727647105</v>
       </c>
@@ -27112,7 +27204,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>727652676</v>
       </c>
@@ -27165,7 +27257,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>727653455</v>
       </c>
@@ -27218,7 +27310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>727658203</v>
       </c>
@@ -27268,7 +27360,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>727661443</v>
       </c>
@@ -27318,7 +27410,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>727664616</v>
       </c>
@@ -27371,7 +27463,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>727667835</v>
       </c>
@@ -27427,7 +27519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>727670481</v>
       </c>
@@ -27477,7 +27569,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>727740627</v>
       </c>
@@ -27527,7 +27619,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>727744299</v>
       </c>
@@ -27583,7 +27675,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>727747282</v>
       </c>
@@ -27636,7 +27728,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>727750230</v>
       </c>
@@ -27692,7 +27784,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>727755155</v>
       </c>
@@ -27745,7 +27837,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>727755338</v>
       </c>
@@ -27798,7 +27890,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>727758680</v>
       </c>
@@ -27851,7 +27943,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>727759452</v>
       </c>
@@ -27904,7 +27996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>727761736</v>
       </c>
@@ -27957,7 +28049,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>727766085</v>
       </c>
@@ -28010,7 +28102,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>727766353</v>
       </c>
@@ -28063,7 +28155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>727769696</v>
       </c>
@@ -28113,7 +28205,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>727771481</v>
       </c>
@@ -28166,7 +28258,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>727774023</v>
       </c>
@@ -28219,7 +28311,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>727778799</v>
       </c>
@@ -28269,7 +28361,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>727782862</v>
       </c>
@@ -28319,7 +28411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>727785231</v>
       </c>
@@ -28372,7 +28464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>727792180</v>
       </c>
@@ -28425,7 +28517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>727795764</v>
       </c>
@@ -28485,16 +28577,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D838C69-485B-49F3-834E-BAB4493306E4}">
-  <dimension ref="A1:K260"/>
-  <sheetFormatPr defaultRowHeight="14.7" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H256"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.35" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -28505,14 +28598,9 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>177</v>
-      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -28520,26 +28608,10 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" ht="18.7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:8" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -28548,206 +28620,88 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="4">
         <f>COUNTA('Dermatoses Bulleuses CNHU HKM'!A:A)-1</f>
         <v>130</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="B10" s="9">
         <f>AVERAGE('Dermatoses Bulleuses CNHU HKM'!F2:F131)</f>
         <v>36.086923076923071</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B11" s="9">
         <f>MEDIAN('Dermatoses Bulleuses CNHU HKM'!F2:F131)</f>
         <v>33</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B12" s="9">
         <f>_xlfn.MODE.SNGL('Dermatoses Bulleuses CNHU HKM'!F2:F131)</f>
         <v>46</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" s="9">
         <f>_xlfn.STDEV.P('Dermatoses Bulleuses CNHU HKM'!F2:F131)</f>
         <v>25.733801143666579</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
@@ -28759,16 +28713,8 @@
         <f>B17/$B$6*100</f>
         <v>56.92307692307692</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -28780,63 +28726,27 @@
         <f>B18/$B$6*100</f>
         <v>43.07692307692308</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -28848,16 +28758,8 @@
         <f>B22/$B$6*100</f>
         <v>52.307692307692314</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -28869,63 +28771,27 @@
         <f>B23/$B$6*100</f>
         <v>47.692307692307693</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
@@ -28937,16 +28803,8 @@
         <f>B27/$B$6*100</f>
         <v>51.538461538461533</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
@@ -28958,16 +28816,8 @@
         <f>B28/$B$6*100</f>
         <v>46.153846153846153</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>58</v>
       </c>
@@ -28979,180 +28829,79 @@
         <f>B29/$B$6*100</f>
         <v>2.3076923076923079</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B32" s="7" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="B33" s="9">
         <f>AVERAGE('Dermatoses Bulleuses CNHU HKM'!N2:N131)</f>
         <v>24.853846153846153</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B34" s="9">
         <f>MEDIAN('Dermatoses Bulleuses CNHU HKM'!N2:N131)</f>
         <v>15</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="9">
         <f>_xlfn.MODE.SNGL('Dermatoses Bulleuses CNHU HKM'!N2:N131)</f>
         <v>10</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" s="9">
         <f>_xlfn.STDEV.P('Dermatoses Bulleuses CNHU HKM'!N2:N131)</f>
         <v>24.846021671475061</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>34</v>
       </c>
@@ -29164,16 +28913,8 @@
         <f>B40/$B$6*100</f>
         <v>54.615384615384613</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>88</v>
       </c>
@@ -29185,16 +28926,8 @@
         <f>B41/$B$6*100</f>
         <v>42.307692307692307</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>73</v>
       </c>
@@ -29206,16 +28939,8 @@
         <f>B42/$B$6*100</f>
         <v>13.846153846153847</v>
       </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>26</v>
       </c>
@@ -29227,63 +28952,27 @@
         <f>B43/$B$6*100</f>
         <v>19.230769230769234</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>19</v>
       </c>
@@ -29295,16 +28984,8 @@
         <f>B47/$B$6*100</f>
         <v>57.692307692307686</v>
       </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>40</v>
       </c>
@@ -29316,16 +28997,8 @@
         <f>B48/$B$6*100</f>
         <v>23.846153846153847</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>28</v>
       </c>
@@ -29337,16 +29010,8 @@
         <f>B49/$B$6*100</f>
         <v>14.615384615384617</v>
       </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>144</v>
       </c>
@@ -29358,63 +29023,27 @@
         <f>B50/$B$6*100</f>
         <v>3.8461538461538463</v>
       </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>44</v>
       </c>
@@ -29426,16 +29055,8 @@
         <f>B54/$B$6*100</f>
         <v>11.538461538461538</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>136</v>
       </c>
@@ -29444,19 +29065,11 @@
         <v>7</v>
       </c>
       <c r="C55" s="9">
-        <f>B55/$B$6*100</f>
+        <f t="shared" ref="C54:C60" si="0">B55/$B$6*100</f>
         <v>5.384615384615385</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>91</v>
       </c>
@@ -29465,19 +29078,11 @@
         <v>3</v>
       </c>
       <c r="C56" s="9">
-        <f>B56/$B$6*100</f>
+        <f t="shared" si="0"/>
         <v>2.3076923076923079</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>41</v>
       </c>
@@ -29486,19 +29091,11 @@
         <v>1</v>
       </c>
       <c r="C57" s="9">
-        <f>B57/$B$6*100</f>
+        <f t="shared" si="0"/>
         <v>0.76923076923076927</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>85</v>
       </c>
@@ -29507,19 +29104,11 @@
         <v>1</v>
       </c>
       <c r="C58" s="9">
-        <f>B58/$B$6*100</f>
+        <f t="shared" si="0"/>
         <v>0.76923076923076927</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>98</v>
       </c>
@@ -29528,19 +29117,11 @@
         <v>1</v>
       </c>
       <c r="C59" s="9">
-        <f>B59/$B$6*100</f>
+        <f t="shared" si="0"/>
         <v>0.76923076923076927</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>47</v>
       </c>
@@ -29549,66 +29130,30 @@
         <v>3</v>
       </c>
       <c r="C60" s="9">
-        <f>B60/$B$6*100</f>
+        <f t="shared" si="0"/>
         <v>2.3076923076923079</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>101</v>
       </c>
@@ -29620,16 +29165,8 @@
         <f>B64/$B$6*100</f>
         <v>7.6923076923076925</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>29</v>
       </c>
@@ -29641,16 +29178,8 @@
         <f>B65/$B$6*100</f>
         <v>2.3076923076923079</v>
       </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>147</v>
       </c>
@@ -29662,16 +29191,8 @@
         <f>B66/$B$6*100</f>
         <v>1.5384615384615385</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>47</v>
       </c>
@@ -29683,63 +29204,27 @@
         <f>B67/$B$6*100</f>
         <v>3.0769230769230771</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>35</v>
       </c>
@@ -29751,16 +29236,8 @@
         <f>B71/$B$6*100</f>
         <v>19.230769230769234</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>74</v>
       </c>
@@ -29772,16 +29249,8 @@
         <f>B72/$B$6*100</f>
         <v>15.384615384615385</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>64</v>
       </c>
@@ -29793,16 +29262,8 @@
         <f>B73/$B$6*100</f>
         <v>11.538461538461538</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>70</v>
       </c>
@@ -29814,16 +29275,8 @@
         <f>B74/$B$6*100</f>
         <v>6.1538461538461542</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>47</v>
       </c>
@@ -29835,161 +29288,62 @@
         <f>B75/$B$6*100</f>
         <v>5.384615384615385</v>
       </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B78" s="7" t="s">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="B79" s="9">
         <f>AVERAGE('Dermatoses Bulleuses CNHU HKM'!J2:J131)</f>
         <v>141.33846153846153</v>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B80" s="9">
         <f>MEDIAN('Dermatoses Bulleuses CNHU HKM'!J2:J131)</f>
         <v>14</v>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B81" s="9">
         <f>_xlfn.MODE.SNGL('Dermatoses Bulleuses CNHU HKM'!J2:J131)</f>
         <v>7</v>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B82" s="9">
         <f>_xlfn.STDEV.P('Dermatoses Bulleuses CNHU HKM'!J2:J131)</f>
         <v>414.8162253678156</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-    </row>
-    <row r="85" spans="1:11" ht="18.7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:8" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -29998,60 +29352,29 @@
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="B89" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;=0",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=18")</f>
@@ -30061,18 +29384,10 @@
         <f>B89/$B$6*100</f>
         <v>33.076923076923073</v>
       </c>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B90" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;18",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=60")</f>
@@ -30082,18 +29397,10 @@
         <f>B90/$B$6*100</f>
         <v>46.92307692307692</v>
       </c>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B91" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
@@ -30103,18 +29410,10 @@
         <f>B91/$B$6*100</f>
         <v>20</v>
       </c>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B92" s="4">
         <f>SUM(B89:B91)</f>
@@ -30124,44 +29423,10 @@
         <f>SUM(C89:C91)</f>
         <v>100</v>
       </c>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-    </row>
-    <row r="95" spans="1:11" ht="16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
@@ -30170,89 +29435,36 @@
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
       <c r="H95" s="10"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B97" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;=0",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=18")</f>
         <v>43</v>
       </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B100" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C100" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>30</v>
       </c>
@@ -30264,16 +29476,8 @@
         <f>IF($B$97&gt;0,B101/$B$97*100,0)</f>
         <v>44.186046511627907</v>
       </c>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>22</v>
       </c>
@@ -30285,63 +29489,27 @@
         <f>IF($B$97&gt;0,B102/$B$97*100,0)</f>
         <v>55.813953488372093</v>
       </c>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B105" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C105" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="4"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>32</v>
       </c>
@@ -30353,16 +29521,8 @@
         <f>IF($B$97&gt;0,B106/$B$97*100,0)</f>
         <v>53.488372093023251</v>
       </c>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>24</v>
       </c>
@@ -30374,63 +29534,27 @@
         <f>IF($B$97&gt;0,B107/$B$97*100,0)</f>
         <v>46.511627906976742</v>
       </c>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B110" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C110" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="4"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>25</v>
       </c>
@@ -30442,16 +29566,8 @@
         <f>IF($B$97&gt;0,B111/$B$97*100,0)</f>
         <v>39.534883720930232</v>
       </c>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>38</v>
       </c>
@@ -30463,16 +29579,8 @@
         <f>IF($B$97&gt;0,B112/$B$97*100,0)</f>
         <v>58.139534883720934</v>
       </c>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="4"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>58</v>
       </c>
@@ -30484,63 +29592,27 @@
         <f>IF($B$97&gt;0,B113/$B$97*100,0)</f>
         <v>2.3255813953488373</v>
       </c>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="4"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
       <c r="D115" s="11"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="4"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C116" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="4"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>19</v>
       </c>
@@ -30552,16 +29624,8 @@
         <f>IF($B$97&gt;0,B117/$B$97*100,0)</f>
         <v>62.790697674418603</v>
       </c>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="4"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>40</v>
       </c>
@@ -30573,16 +29637,8 @@
         <f>IF($B$97&gt;0,B118/$B$97*100,0)</f>
         <v>4.6511627906976747</v>
       </c>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
-      <c r="K118" s="4"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>28</v>
       </c>
@@ -30594,16 +29650,8 @@
         <f>IF($B$97&gt;0,B119/$B$97*100,0)</f>
         <v>30.232558139534881</v>
       </c>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="4"/>
-      <c r="K119" s="4"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>144</v>
       </c>
@@ -30615,44 +29663,10 @@
         <f>IF($B$97&gt;0,B120/$B$97*100,0)</f>
         <v>2.3255813953488373</v>
       </c>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-      <c r="J120" s="4"/>
-      <c r="K120" s="4"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="4"/>
-      <c r="K121" s="4"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
-      <c r="K122" s="4"/>
-    </row>
-    <row r="123" spans="1:11" ht="16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -30661,89 +29675,36 @@
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
-      <c r="K123" s="4"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-      <c r="J124" s="4"/>
-      <c r="K124" s="4"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B125" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;18",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=60")</f>
         <v>61</v>
       </c>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="4"/>
-      <c r="K125" s="4"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-      <c r="J126" s="4"/>
-      <c r="K126" s="4"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B127" s="13"/>
       <c r="C127" s="13"/>
       <c r="D127" s="13"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B128" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C128" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C128" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-      <c r="J128" s="4"/>
-      <c r="K128" s="4"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>30</v>
       </c>
@@ -30755,16 +29716,8 @@
         <f>IF($B$125&gt;0,B129/$B$125*100,0)</f>
         <v>65.573770491803273</v>
       </c>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="4"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>22</v>
       </c>
@@ -30776,63 +29729,27 @@
         <f>IF($B$125&gt;0,B130/$B$125*100,0)</f>
         <v>34.42622950819672</v>
       </c>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="4"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="4"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B132" s="13"/>
       <c r="C132" s="13"/>
       <c r="D132" s="13"/>
-      <c r="E132" s="4"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="4"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B133" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C133" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="4"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>32</v>
       </c>
@@ -30844,16 +29761,8 @@
         <f>IF($B$125&gt;0,B134/$B$125*100,0)</f>
         <v>62.295081967213115</v>
       </c>
-      <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
-      <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="4"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>24</v>
       </c>
@@ -30865,63 +29774,27 @@
         <f>IF($B$125&gt;0,B135/$B$125*100,0)</f>
         <v>37.704918032786885</v>
       </c>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
-      <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="4"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B137" s="13"/>
       <c r="C137" s="13"/>
       <c r="D137" s="13"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B138" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C138" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C138" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>25</v>
       </c>
@@ -30933,16 +29806,8 @@
         <f>IF($B$125&gt;0,B139/$B$125*100,0)</f>
         <v>52.459016393442624</v>
       </c>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
-      <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
-      <c r="K139" s="4"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>38</v>
       </c>
@@ -30954,16 +29819,8 @@
         <f>IF($B$125&gt;0,B140/$B$125*100,0)</f>
         <v>47.540983606557376</v>
       </c>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-      <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="4"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>58</v>
       </c>
@@ -30975,63 +29832,27 @@
         <f>IF($B$125&gt;0,B141/$B$125*100,0)</f>
         <v>0</v>
       </c>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
-      <c r="K141" s="4"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
-      <c r="K142" s="4"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B143" s="13"/>
       <c r="C143" s="13"/>
       <c r="D143" s="13"/>
-      <c r="E143" s="4"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="4"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C144" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C144" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
-      <c r="K144" s="4"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>19</v>
       </c>
@@ -31043,16 +29864,8 @@
         <f>IF($B$125&gt;0,B145/$B$125*100,0)</f>
         <v>65.573770491803273</v>
       </c>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
-      <c r="K145" s="4"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>40</v>
       </c>
@@ -31064,16 +29877,8 @@
         <f>IF($B$125&gt;0,B146/$B$125*100,0)</f>
         <v>19.672131147540984</v>
       </c>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="4"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>28</v>
       </c>
@@ -31085,16 +29890,8 @@
         <f>IF($B$125&gt;0,B147/$B$125*100,0)</f>
         <v>8.1967213114754092</v>
       </c>
-      <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
-      <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
-      <c r="K147" s="4"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>144</v>
       </c>
@@ -31106,44 +29903,10 @@
         <f>IF($B$125&gt;0,B148/$B$125*100,0)</f>
         <v>6.557377049180328</v>
       </c>
-      <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="4"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
-      <c r="K149" s="4"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
-      <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
-      <c r="K150" s="4"/>
-    </row>
-    <row r="151" spans="1:11" ht="16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A151" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -31152,89 +29915,36 @@
       <c r="F151" s="14"/>
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
-      <c r="K151" s="4"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="4"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B153" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
         <v>26</v>
       </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
-      <c r="K153" s="4"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
       <c r="D155" s="15"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B156" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C156" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C156" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>30</v>
       </c>
@@ -31246,16 +29956,8 @@
         <f>IF($B$153&gt;0,B157/$B$153*100,0)</f>
         <v>57.692307692307686</v>
       </c>
-      <c r="D157" s="4"/>
-      <c r="E157" s="4"/>
-      <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>22</v>
       </c>
@@ -31267,63 +29969,27 @@
         <f>IF($B$153&gt;0,B158/$B$153*100,0)</f>
         <v>42.307692307692307</v>
       </c>
-      <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
-      <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
-      <c r="K158" s="4"/>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
-      <c r="K159" s="4"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
       <c r="D160" s="15"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="4"/>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B161" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C161" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C161" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D161" s="4"/>
-      <c r="E161" s="4"/>
-      <c r="F161" s="4"/>
-      <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
-      <c r="K161" s="4"/>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>32</v>
       </c>
@@ -31335,16 +30001,8 @@
         <f>IF($B$153&gt;0,B162/$B$153*100,0)</f>
         <v>26.923076923076923</v>
       </c>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4"/>
-      <c r="F162" s="4"/>
-      <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
-      <c r="I162" s="4"/>
-      <c r="J162" s="4"/>
-      <c r="K162" s="4"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>24</v>
       </c>
@@ -31356,63 +30014,27 @@
         <f>IF($B$153&gt;0,B163/$B$153*100,0)</f>
         <v>73.076923076923066</v>
       </c>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
-      <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
-      <c r="K163" s="4"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
-      <c r="K164" s="4"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
       <c r="D165" s="15"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="4"/>
-      <c r="K165" s="4"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B166" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C166" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C166" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="4"/>
-      <c r="J166" s="4"/>
-      <c r="K166" s="4"/>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>25</v>
       </c>
@@ -31424,16 +30046,8 @@
         <f>IF($B$153&gt;0,B167/$B$153*100,0)</f>
         <v>69.230769230769226</v>
       </c>
-      <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
-      <c r="K167" s="4"/>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>38</v>
       </c>
@@ -31445,16 +30059,8 @@
         <f>IF($B$153&gt;0,B168/$B$153*100,0)</f>
         <v>23.076923076923077</v>
       </c>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
-      <c r="K168" s="4"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>58</v>
       </c>
@@ -31466,63 +30072,27 @@
         <f>IF($B$153&gt;0,B169/$B$153*100,0)</f>
         <v>7.6923076923076925</v>
       </c>
-      <c r="D169" s="4"/>
-      <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
-      <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="4"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-      <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
-      <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
-      <c r="K170" s="4"/>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
       <c r="D171" s="15"/>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
-      <c r="K171" s="4"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B172" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C172" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C172" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D172" s="4"/>
-      <c r="E172" s="4"/>
-      <c r="F172" s="4"/>
-      <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
-      <c r="I172" s="4"/>
-      <c r="J172" s="4"/>
-      <c r="K172" s="4"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>19</v>
       </c>
@@ -31534,16 +30104,8 @@
         <f>IF($B$153&gt;0,B173/$B$153*100,0)</f>
         <v>30.76923076923077</v>
       </c>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-      <c r="I173" s="4"/>
-      <c r="J173" s="4"/>
-      <c r="K173" s="4"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>40</v>
       </c>
@@ -31555,16 +30117,8 @@
         <f>IF($B$153&gt;0,B174/$B$153*100,0)</f>
         <v>65.384615384615387</v>
       </c>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
-      <c r="K174" s="4"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>28</v>
       </c>
@@ -31576,16 +30130,8 @@
         <f>IF($B$153&gt;0,B175/$B$153*100,0)</f>
         <v>3.8461538461538463</v>
       </c>
-      <c r="D175" s="4"/>
-      <c r="E175" s="4"/>
-      <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
-      <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
-      <c r="K175" s="4"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>144</v>
       </c>
@@ -31597,44 +30143,10 @@
         <f>IF($B$153&gt;0,B176/$B$153*100,0)</f>
         <v>0</v>
       </c>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
-      <c r="K176" s="4"/>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="4"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A178" s="4"/>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="4"/>
-    </row>
-    <row r="179" spans="1:11" ht="18.7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:8" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -31643,26 +30155,10 @@
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
-      <c r="I179" s="4"/>
-      <c r="J179" s="4"/>
-      <c r="K179" s="4"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-      <c r="E180" s="4"/>
-      <c r="F180" s="4"/>
-      <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="4"/>
-      <c r="J180" s="4"/>
-      <c r="K180" s="4"/>
-    </row>
-    <row r="181" spans="1:11" ht="16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A181" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B181" s="16"/>
       <c r="C181" s="16"/>
@@ -31671,91 +30167,38 @@
       <c r="F181" s="16"/>
       <c r="G181" s="16"/>
       <c r="H181" s="16"/>
-      <c r="I181" s="4"/>
-      <c r="J181" s="4"/>
-      <c r="K181" s="4"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
-      <c r="I182" s="4"/>
-      <c r="J182" s="4"/>
-      <c r="K182" s="4"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B183" s="4">
         <f>COUNTIF('Dermatoses Bulleuses CNHU HKM'!G:G,"Femme")</f>
         <v>74</v>
       </c>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-      <c r="E183" s="4"/>
-      <c r="F183" s="4"/>
-      <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
-      <c r="I183" s="4"/>
-      <c r="J183" s="4"/>
-      <c r="K183" s="4"/>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
-      <c r="D184" s="4"/>
-      <c r="E184" s="4"/>
-      <c r="F184" s="4"/>
-      <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
-      <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
-      <c r="K184" s="4"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D186" s="4"/>
-      <c r="E186" s="4"/>
-      <c r="F186" s="4"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
-      <c r="K186" s="4"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="B187" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Femme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;=0",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=18")</f>
@@ -31765,18 +30208,10 @@
         <f>IF($B$183&gt;0,B187/$B$183*100,0)</f>
         <v>25.675675675675674</v>
       </c>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-      <c r="I187" s="4"/>
-      <c r="J187" s="4"/>
-      <c r="K187" s="4"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B188" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Femme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;18",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=60")</f>
@@ -31786,18 +30221,10 @@
         <f>IF($B$183&gt;0,B188/$B$183*100,0)</f>
         <v>54.054054054054056</v>
       </c>
-      <c r="D188" s="4"/>
-      <c r="E188" s="4"/>
-      <c r="F188" s="4"/>
-      <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
-      <c r="K188" s="4"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B189" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Femme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
@@ -31807,63 +30234,27 @@
         <f>IF($B$183&gt;0,B189/$B$183*100,0)</f>
         <v>20.27027027027027</v>
       </c>
-      <c r="D189" s="4"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="4"/>
-      <c r="J189" s="4"/>
-      <c r="K189" s="4"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A190" s="4"/>
-      <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
-      <c r="D190" s="4"/>
-      <c r="E190" s="4"/>
-      <c r="F190" s="4"/>
-      <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
-      <c r="K190" s="4"/>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="4"/>
-      <c r="J191" s="4"/>
-      <c r="K191" s="4"/>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B192" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C192" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C192" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D192" s="4"/>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
-      <c r="K192" s="4"/>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>32</v>
       </c>
@@ -31875,16 +30266,8 @@
         <f>IF($B$183&gt;0,B193/$B$183*100,0)</f>
         <v>52.702702702702695</v>
       </c>
-      <c r="D193" s="4"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-      <c r="I193" s="4"/>
-      <c r="J193" s="4"/>
-      <c r="K193" s="4"/>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>24</v>
       </c>
@@ -31896,63 +30279,27 @@
         <f>IF($B$183&gt;0,B194/$B$183*100,0)</f>
         <v>47.297297297297298</v>
       </c>
-      <c r="D194" s="4"/>
-      <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A195" s="4"/>
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
-      <c r="K195" s="4"/>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
-      <c r="E196" s="4"/>
-      <c r="F196" s="4"/>
-      <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B197" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C197" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C197" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-      <c r="I197" s="4"/>
-      <c r="J197" s="4"/>
-      <c r="K197" s="4"/>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>25</v>
       </c>
@@ -31964,16 +30311,8 @@
         <f>IF($B$183&gt;0,B198/$B$183*100,0)</f>
         <v>59.45945945945946</v>
       </c>
-      <c r="D198" s="4"/>
-      <c r="E198" s="4"/>
-      <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
-      <c r="K198" s="4"/>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>38</v>
       </c>
@@ -31985,16 +30324,8 @@
         <f>IF($B$183&gt;0,B199/$B$183*100,0)</f>
         <v>40.54054054054054</v>
       </c>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
-      <c r="I199" s="4"/>
-      <c r="J199" s="4"/>
-      <c r="K199" s="4"/>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>58</v>
       </c>
@@ -32006,63 +30337,27 @@
         <f>IF($B$183&gt;0,B200/$B$183*100,0)</f>
         <v>0</v>
       </c>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
-      <c r="J200" s="4"/>
-      <c r="K200" s="4"/>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="4"/>
-      <c r="J201" s="4"/>
-      <c r="K201" s="4"/>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
-      <c r="I202" s="4"/>
-      <c r="J202" s="4"/>
-      <c r="K202" s="4"/>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B203" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C203" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C203" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D203" s="4"/>
-      <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
-      <c r="H203" s="4"/>
-      <c r="I203" s="4"/>
-      <c r="J203" s="4"/>
-      <c r="K203" s="4"/>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>19</v>
       </c>
@@ -32074,16 +30369,8 @@
         <f>IF($B$183&gt;0,B204/$B$183*100,0)</f>
         <v>58.108108108108105</v>
       </c>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
-      <c r="I204" s="4"/>
-      <c r="J204" s="4"/>
-      <c r="K204" s="4"/>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>40</v>
       </c>
@@ -32095,16 +30382,8 @@
         <f>IF($B$183&gt;0,B205/$B$183*100,0)</f>
         <v>28.378378378378379</v>
       </c>
-      <c r="D205" s="4"/>
-      <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
-      <c r="I205" s="4"/>
-      <c r="J205" s="4"/>
-      <c r="K205" s="4"/>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>28</v>
       </c>
@@ -32116,16 +30395,8 @@
         <f>IF($B$183&gt;0,B206/$B$183*100,0)</f>
         <v>9.4594594594594597</v>
       </c>
-      <c r="D206" s="4"/>
-      <c r="E206" s="4"/>
-      <c r="F206" s="4"/>
-      <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
-      <c r="I206" s="4"/>
-      <c r="J206" s="4"/>
-      <c r="K206" s="4"/>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>144</v>
       </c>
@@ -32137,44 +30408,10 @@
         <f>IF($B$183&gt;0,B207/$B$183*100,0)</f>
         <v>4.0540540540540544</v>
       </c>
-      <c r="D207" s="4"/>
-      <c r="E207" s="4"/>
-      <c r="F207" s="4"/>
-      <c r="G207" s="4"/>
-      <c r="H207" s="4"/>
-      <c r="I207" s="4"/>
-      <c r="J207" s="4"/>
-      <c r="K207" s="4"/>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-      <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
-      <c r="I208" s="4"/>
-      <c r="J208" s="4"/>
-      <c r="K208" s="4"/>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A209" s="4"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
-      <c r="I209" s="4"/>
-      <c r="J209" s="4"/>
-      <c r="K209" s="4"/>
-    </row>
-    <row r="210" spans="1:11" ht="16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A210" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B210" s="18"/>
       <c r="C210" s="18"/>
@@ -32183,91 +30420,38 @@
       <c r="F210" s="18"/>
       <c r="G210" s="18"/>
       <c r="H210" s="18"/>
-      <c r="I210" s="4"/>
-      <c r="J210" s="4"/>
-      <c r="K210" s="4"/>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A211" s="4"/>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
-      <c r="J211" s="4"/>
-      <c r="K211" s="4"/>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B212" s="4">
         <f>COUNTIF('Dermatoses Bulleuses CNHU HKM'!G:G,"Homme")</f>
         <v>56</v>
       </c>
-      <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-      <c r="E212" s="4"/>
-      <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
-      <c r="H212" s="4"/>
-      <c r="I212" s="4"/>
-      <c r="J212" s="4"/>
-      <c r="K212" s="4"/>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A213" s="4"/>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
-      <c r="H213" s="4"/>
-      <c r="I213" s="4"/>
-      <c r="J213" s="4"/>
-      <c r="K213" s="4"/>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B214" s="19"/>
       <c r="C214" s="19"/>
       <c r="D214" s="19"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
-      <c r="I214" s="4"/>
-      <c r="J214" s="4"/>
-      <c r="K214" s="4"/>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D215" s="4"/>
-      <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
-      <c r="G215" s="4"/>
-      <c r="H215" s="4"/>
-      <c r="I215" s="4"/>
-      <c r="J215" s="4"/>
-      <c r="K215" s="4"/>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A216" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="B216" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Homme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;=0",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=18")</f>
@@ -32277,18 +30461,10 @@
         <f>IF($B$212&gt;0,B216/$B$212*100,0)</f>
         <v>42.857142857142854</v>
       </c>
-      <c r="D216" s="4"/>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
-      <c r="I216" s="4"/>
-      <c r="J216" s="4"/>
-      <c r="K216" s="4"/>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B217" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Homme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;18",'Dermatoses Bulleuses CNHU HKM'!F:F,"&lt;=60")</f>
@@ -32298,18 +30474,10 @@
         <f>IF($B$212&gt;0,B217/$B$212*100,0)</f>
         <v>37.5</v>
       </c>
-      <c r="D217" s="4"/>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="4"/>
-      <c r="I217" s="4"/>
-      <c r="J217" s="4"/>
-      <c r="K217" s="4"/>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B218" s="4">
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Homme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
@@ -32319,63 +30487,27 @@
         <f>IF($B$212&gt;0,B218/$B$212*100,0)</f>
         <v>19.642857142857142</v>
       </c>
-      <c r="D218" s="4"/>
-      <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
-      <c r="J218" s="4"/>
-      <c r="K218" s="4"/>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A219" s="4"/>
-      <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
-      <c r="D219" s="4"/>
-      <c r="E219" s="4"/>
-      <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
-      <c r="H219" s="4"/>
-      <c r="I219" s="4"/>
-      <c r="J219" s="4"/>
-      <c r="K219" s="4"/>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B220" s="19"/>
       <c r="C220" s="19"/>
       <c r="D220" s="19"/>
-      <c r="E220" s="4"/>
-      <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
-      <c r="H220" s="4"/>
-      <c r="I220" s="4"/>
-      <c r="J220" s="4"/>
-      <c r="K220" s="4"/>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B221" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C221" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C221" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D221" s="4"/>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4"/>
-      <c r="G221" s="4"/>
-      <c r="H221" s="4"/>
-      <c r="I221" s="4"/>
-      <c r="J221" s="4"/>
-      <c r="K221" s="4"/>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>32</v>
       </c>
@@ -32387,16 +30519,8 @@
         <f>IF($B$212&gt;0,B222/$B$212*100,0)</f>
         <v>51.785714285714292</v>
       </c>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
-      <c r="J222" s="4"/>
-      <c r="K222" s="4"/>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>24</v>
       </c>
@@ -32408,63 +30532,27 @@
         <f>IF($B$212&gt;0,B223/$B$212*100,0)</f>
         <v>48.214285714285715</v>
       </c>
-      <c r="D223" s="4"/>
-      <c r="E223" s="4"/>
-      <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
-      <c r="I223" s="4"/>
-      <c r="J223" s="4"/>
-      <c r="K223" s="4"/>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A224" s="4"/>
-      <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
-      <c r="D224" s="4"/>
-      <c r="E224" s="4"/>
-      <c r="F224" s="4"/>
-      <c r="G224" s="4"/>
-      <c r="H224" s="4"/>
-      <c r="I224" s="4"/>
-      <c r="J224" s="4"/>
-      <c r="K224" s="4"/>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B225" s="19"/>
       <c r="C225" s="19"/>
       <c r="D225" s="19"/>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
-      <c r="J225" s="4"/>
-      <c r="K225" s="4"/>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B226" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C226" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C226" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D226" s="4"/>
-      <c r="E226" s="4"/>
-      <c r="F226" s="4"/>
-      <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
-      <c r="I226" s="4"/>
-      <c r="J226" s="4"/>
-      <c r="K226" s="4"/>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>25</v>
       </c>
@@ -32476,16 +30564,8 @@
         <f>IF($B$212&gt;0,B227/$B$212*100,0)</f>
         <v>41.071428571428569</v>
       </c>
-      <c r="D227" s="4"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
-      <c r="I227" s="4"/>
-      <c r="J227" s="4"/>
-      <c r="K227" s="4"/>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>38</v>
       </c>
@@ -32497,16 +30577,8 @@
         <f>IF($B$212&gt;0,B228/$B$212*100,0)</f>
         <v>53.571428571428569</v>
       </c>
-      <c r="D228" s="4"/>
-      <c r="E228" s="4"/>
-      <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
-      <c r="I228" s="4"/>
-      <c r="J228" s="4"/>
-      <c r="K228" s="4"/>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>58</v>
       </c>
@@ -32518,63 +30590,27 @@
         <f>IF($B$212&gt;0,B229/$B$212*100,0)</f>
         <v>5.3571428571428568</v>
       </c>
-      <c r="D229" s="4"/>
-      <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
-      <c r="H229" s="4"/>
-      <c r="I229" s="4"/>
-      <c r="J229" s="4"/>
-      <c r="K229" s="4"/>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A230" s="4"/>
-      <c r="B230" s="4"/>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-      <c r="E230" s="4"/>
-      <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
-      <c r="I230" s="4"/>
-      <c r="J230" s="4"/>
-      <c r="K230" s="4"/>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B231" s="19"/>
       <c r="C231" s="19"/>
       <c r="D231" s="19"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
-      <c r="I231" s="4"/>
-      <c r="J231" s="4"/>
-      <c r="K231" s="4"/>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B232" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C232" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C232" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D232" s="4"/>
-      <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
-      <c r="I232" s="4"/>
-      <c r="J232" s="4"/>
-      <c r="K232" s="4"/>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>19</v>
       </c>
@@ -32586,16 +30622,8 @@
         <f>IF($B$212&gt;0,B233/$B$212*100,0)</f>
         <v>57.142857142857139</v>
       </c>
-      <c r="D233" s="4"/>
-      <c r="E233" s="4"/>
-      <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
-      <c r="H233" s="4"/>
-      <c r="I233" s="4"/>
-      <c r="J233" s="4"/>
-      <c r="K233" s="4"/>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>40</v>
       </c>
@@ -32607,16 +30635,8 @@
         <f>IF($B$212&gt;0,B234/$B$212*100,0)</f>
         <v>17.857142857142858</v>
       </c>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="4"/>
-      <c r="J234" s="4"/>
-      <c r="K234" s="4"/>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>28</v>
       </c>
@@ -32628,16 +30648,8 @@
         <f>IF($B$212&gt;0,B235/$B$212*100,0)</f>
         <v>21.428571428571427</v>
       </c>
-      <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
-      <c r="H235" s="4"/>
-      <c r="I235" s="4"/>
-      <c r="J235" s="4"/>
-      <c r="K235" s="4"/>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>144</v>
       </c>
@@ -32649,44 +30661,10 @@
         <f>IF($B$212&gt;0,B236/$B$212*100,0)</f>
         <v>3.5714285714285712</v>
       </c>
-      <c r="D236" s="4"/>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
-      <c r="H236" s="4"/>
-      <c r="I236" s="4"/>
-      <c r="J236" s="4"/>
-      <c r="K236" s="4"/>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A237" s="4"/>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
-      <c r="H237" s="4"/>
-      <c r="I237" s="4"/>
-      <c r="J237" s="4"/>
-      <c r="K237" s="4"/>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="4"/>
-      <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
-      <c r="E238" s="4"/>
-      <c r="F238" s="4"/>
-      <c r="G238" s="4"/>
-      <c r="H238" s="4"/>
-      <c r="I238" s="4"/>
-      <c r="J238" s="4"/>
-      <c r="K238" s="4"/>
-    </row>
-    <row r="239" spans="1:11" ht="18.7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:8" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A239" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B239" s="6"/>
       <c r="C239" s="6"/>
@@ -32695,43 +30673,20 @@
       <c r="F239" s="6"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
-      <c r="I239" s="4"/>
-      <c r="J239" s="4"/>
-      <c r="K239" s="4"/>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A240" s="4"/>
-      <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="4"/>
-      <c r="E240" s="4"/>
-      <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
-      <c r="H240" s="4"/>
-      <c r="I240" s="4"/>
-      <c r="J240" s="4"/>
-      <c r="K240" s="4"/>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C241" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="C241" s="20" t="s">
+      <c r="D241" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="D241" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="E241" s="4"/>
-      <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
-      <c r="H241" s="4"/>
-      <c r="I241" s="4"/>
-      <c r="J241" s="4"/>
-      <c r="K241" s="4"/>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>30</v>
       </c>
@@ -32747,15 +30702,8 @@
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Femme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
         <v>15</v>
       </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
-      <c r="I242" s="4"/>
-      <c r="J242" s="4"/>
-      <c r="K242" s="4"/>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>22</v>
       </c>
@@ -32771,17 +30719,10 @@
         <f>COUNTIFS('Dermatoses Bulleuses CNHU HKM'!G:G,"Homme",'Dermatoses Bulleuses CNHU HKM'!F:F,"&gt;60")</f>
         <v>11</v>
       </c>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
-      <c r="H243" s="4"/>
-      <c r="I243" s="4"/>
-      <c r="J243" s="4"/>
-      <c r="K243" s="4"/>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B244" s="4">
         <f>SUM(B242:B243)</f>
@@ -32795,79 +30736,34 @@
         <f>SUM(D242:D243)</f>
         <v>26</v>
       </c>
-      <c r="E244" s="4"/>
-      <c r="F244" s="4"/>
-      <c r="G244" s="4"/>
-      <c r="H244" s="4"/>
-      <c r="I244" s="4"/>
-      <c r="J244" s="4"/>
-      <c r="K244" s="4"/>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A245" s="4"/>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
-      <c r="H245" s="4"/>
-      <c r="I245" s="4"/>
-      <c r="J245" s="4"/>
-      <c r="K245" s="4"/>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
-      <c r="I246" s="4"/>
-      <c r="J246" s="4"/>
-      <c r="K246" s="4"/>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
       <c r="D247" s="8"/>
       <c r="E247" s="8"/>
-      <c r="F247" s="4"/>
-      <c r="G247" s="4"/>
-      <c r="H247" s="4"/>
-      <c r="I247" s="4"/>
-      <c r="J247" s="4"/>
-      <c r="K247" s="4"/>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B248" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C248" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C248" s="7" t="s">
+      <c r="D248" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D248" s="7" t="s">
-        <v>204</v>
-      </c>
       <c r="E248" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
-      <c r="H248" s="4"/>
-      <c r="I248" s="4"/>
-      <c r="J248" s="4"/>
-      <c r="K248" s="4"/>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>19</v>
       </c>
@@ -32887,14 +30783,8 @@
         <f>SUM(B249:D249)</f>
         <v>75</v>
       </c>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="4"/>
-      <c r="J249" s="4"/>
-      <c r="K249" s="4"/>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>40</v>
       </c>
@@ -32914,14 +30804,8 @@
         <f>SUM(B250:D250)</f>
         <v>31</v>
       </c>
-      <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
-      <c r="I250" s="4"/>
-      <c r="J250" s="4"/>
-      <c r="K250" s="4"/>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>28</v>
       </c>
@@ -32941,14 +30825,8 @@
         <f>SUM(B251:D251)</f>
         <v>19</v>
       </c>
-      <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
-      <c r="H251" s="4"/>
-      <c r="I251" s="4"/>
-      <c r="J251" s="4"/>
-      <c r="K251" s="4"/>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>144</v>
       </c>
@@ -32968,16 +30846,10 @@
         <f>SUM(B252:D252)</f>
         <v>5</v>
       </c>
-      <c r="F252" s="4"/>
-      <c r="G252" s="4"/>
-      <c r="H252" s="4"/>
-      <c r="I252" s="4"/>
-      <c r="J252" s="4"/>
-      <c r="K252" s="4"/>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B253" s="4">
         <f>SUM(B249:B252)</f>
@@ -32995,40 +30867,8 @@
         <f>SUM(E249:E252)</f>
         <v>130</v>
       </c>
-      <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
-      <c r="H253" s="4"/>
-      <c r="I253" s="4"/>
-      <c r="J253" s="4"/>
-      <c r="K253" s="4"/>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A254" s="4"/>
-      <c r="B254" s="4"/>
-      <c r="C254" s="4"/>
-      <c r="D254" s="4"/>
-      <c r="E254" s="4"/>
-      <c r="F254" s="4"/>
-      <c r="G254" s="4"/>
-      <c r="H254" s="4"/>
-      <c r="I254" s="4"/>
-      <c r="J254" s="4"/>
-      <c r="K254" s="4"/>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A255" s="4"/>
-      <c r="B255" s="4"/>
-      <c r="C255" s="4"/>
-      <c r="D255" s="4"/>
-      <c r="E255" s="4"/>
-      <c r="F255" s="4"/>
-      <c r="G255" s="4"/>
-      <c r="H255" s="4"/>
-      <c r="I255" s="4"/>
-      <c r="J255" s="4"/>
-      <c r="K255" s="4"/>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="21"/>
       <c r="B256" s="21"/>
       <c r="C256" s="21"/>
@@ -33037,64 +30877,45 @@
       <c r="F256" s="21"/>
       <c r="G256" s="21"/>
       <c r="H256" s="21"/>
-      <c r="I256" s="4"/>
-      <c r="J256" s="4"/>
-      <c r="K256" s="4"/>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A257" s="4"/>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="4"/>
-      <c r="G257" s="4"/>
-      <c r="H257" s="4"/>
-      <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
-      <c r="K257" s="4"/>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A258" s="4"/>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
-      <c r="I258" s="4"/>
-      <c r="J258" s="4"/>
-      <c r="K258" s="4"/>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A259" s="4"/>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
-      <c r="H259" s="4"/>
-      <c r="I259" s="4"/>
-      <c r="J259" s="4"/>
-      <c r="K259" s="4"/>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A260" s="4"/>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
-      <c r="G260" s="4"/>
-      <c r="H260" s="4"/>
-      <c r="I260" s="4"/>
-      <c r="J260" s="4"/>
-      <c r="K260" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A123:H123"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A151:H151"/>
+    <mergeCell ref="A155:D155"/>
+    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A165:D165"/>
+    <mergeCell ref="A171:D171"/>
+    <mergeCell ref="A179:H179"/>
+    <mergeCell ref="A181:H181"/>
+    <mergeCell ref="A185:D185"/>
+    <mergeCell ref="A191:D191"/>
     <mergeCell ref="A239:H239"/>
     <mergeCell ref="A247:E247"/>
     <mergeCell ref="A256:H256"/>
@@ -33104,45 +30925,10 @@
     <mergeCell ref="A220:D220"/>
     <mergeCell ref="A225:D225"/>
     <mergeCell ref="A231:D231"/>
-    <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A179:H179"/>
-    <mergeCell ref="A181:H181"/>
-    <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A191:D191"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A151:H151"/>
-    <mergeCell ref="A155:D155"/>
-    <mergeCell ref="A160:D160"/>
-    <mergeCell ref="A165:D165"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A109:D109"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A123:H123"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
